--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подписи" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клеммы" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модули ПЛК" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каналы ПЛК" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -562,26 +564,59 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Литера</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Суффикс схемы</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Э3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Масса</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Название схемы</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Схема электрическая принципиальная</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Первый лист ПЛК в схеме</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Литера</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Масса</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -659,8 +694,6 @@
           <t>Т.контр.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -668,8 +701,6 @@
           <t>Нач.отд.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -677,8 +708,6 @@
           <t>Н.контр.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -775,7 +804,6 @@
           <t>INOVANCE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -801,7 +829,6 @@
           <t>INOVANCE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -827,7 +854,6 @@
           <t>INOVANCE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -853,7 +879,6 @@
           <t>КИТ ЭНЕРГО</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -879,7 +904,6 @@
           <t>Klemsan</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -905,7 +929,6 @@
           <t>Klemsan</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -931,7 +954,6 @@
           <t>Klemsan</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -957,7 +979,6 @@
           <t>Klemsan</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -983,7 +1004,6 @@
           <t>Klemsan</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1009,7 +1029,6 @@
           <t>STEZ</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1035,7 +1054,6 @@
           <t>Fortisflex</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1061,7 +1079,6 @@
           <t>Fortisflex</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1087,7 +1104,6 @@
           <t>Natclic</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1113,7 +1129,6 @@
           <t>Natclic</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1139,7 +1154,6 @@
           <t>Natclic</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1165,7 +1179,6 @@
           <t>MOXA</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1191,7 +1204,6 @@
           <t>MOXA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1217,7 +1229,6 @@
           <t>Wiedmuller</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1243,7 +1254,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1269,7 +1279,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1295,7 +1304,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1321,7 +1329,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1347,7 +1354,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1373,7 +1379,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1399,7 +1404,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1425,7 +1429,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1451,7 +1454,6 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1477,7 +1479,6 @@
           <t>FINDER</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1503,7 +1504,6 @@
           <t>FINDER</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1529,7 +1529,6 @@
           <t>FINDER</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1555,7 +1554,6 @@
           <t>FINDER</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1581,7 +1579,6 @@
           <t>IFC</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1607,7 +1604,6 @@
           <t>IFC</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1633,7 +1629,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1659,7 +1654,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1685,7 +1679,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1711,7 +1704,6 @@
           <t>DEKraft</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1737,7 +1729,6 @@
           <t>DEKraft</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1763,7 +1754,6 @@
           <t>DEKraft</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1789,7 +1779,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1815,7 +1804,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1841,7 +1829,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1867,7 +1854,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1893,7 +1879,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1919,7 +1904,6 @@
           <t>Systeme Electric</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1945,7 +1929,6 @@
           <t>Natclic</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1971,7 +1954,6 @@
           <t>Wiedmuller</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1997,7 +1979,6 @@
           <t>Wiedmuller</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2004,6 @@
           <t>CABEUS</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2049,7 +2029,6 @@
           <t>CABEUS</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2075,7 +2054,6 @@
           <t>FLEXICORE</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2101,7 +2079,6 @@
           <t>ExeGate</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2127,7 +2104,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2153,7 +2129,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2179,7 +2154,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2205,7 +2179,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2231,7 +2204,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2257,7 +2229,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2283,7 +2254,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2309,7 +2279,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2335,7 +2304,6 @@
           <t>NIKOMAX</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2361,7 +2329,6 @@
           <t>CABEUS</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2387,7 +2354,6 @@
           <t>FUCON</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2413,7 +2379,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2439,7 +2404,6 @@
           <t>ConnectWell</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2465,7 +2429,6 @@
           <t>IEK</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2491,7 +2454,6 @@
           <t>CHINT</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2517,7 +2479,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2543,7 +2504,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2569,7 +2529,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2595,7 +2554,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2621,7 +2579,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2647,7 +2604,6 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2673,7 +2629,6 @@
           <t>FUCON</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2774,9 +2729,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>L1</t>
@@ -2785,7 +2737,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2808,9 +2759,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>L2</t>
@@ -2819,7 +2767,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2842,9 +2789,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>L3</t>
@@ -2853,7 +2797,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2876,9 +2819,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2887,7 +2827,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2910,9 +2849,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>PE</t>
@@ -2921,7 +2857,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2944,9 +2879,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>PE</t>
@@ -2955,7 +2887,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2973,13 +2904,6 @@
           <t>EPCX4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3002,9 +2926,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>L</t>
@@ -3013,7 +2934,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3036,9 +2956,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>N</t>
@@ -3047,7 +2964,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3070,9 +2986,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3081,7 +2994,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3099,13 +3011,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3128,9 +3033,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>1</t>
@@ -3139,7 +3041,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3162,9 +3063,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>2</t>
@@ -3173,7 +3071,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3196,9 +3093,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>3</t>
@@ -3207,7 +3101,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3230,9 +3123,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>4</t>
@@ -3241,7 +3131,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3259,13 +3148,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3288,9 +3170,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>1L+</t>
@@ -3324,9 +3203,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>1L+</t>
@@ -3360,9 +3236,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>1M</t>
@@ -3396,9 +3269,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>1M</t>
@@ -3432,9 +3302,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>2L+</t>
@@ -3443,7 +3310,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3466,9 +3332,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>2M</t>
@@ -3477,7 +3340,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3495,13 +3357,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3524,9 +3379,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>L</t>
@@ -3535,7 +3387,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3558,9 +3409,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>N</t>
@@ -3569,7 +3417,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3592,9 +3439,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3603,7 +3447,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3621,13 +3464,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3650,9 +3486,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>L</t>
@@ -3661,7 +3494,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3684,9 +3516,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>N</t>
@@ -3695,7 +3524,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3718,9 +3546,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3729,7 +3554,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3747,13 +3571,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3776,9 +3593,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>L</t>
@@ -3787,7 +3601,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3810,9 +3623,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>N</t>
@@ -3821,7 +3631,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3844,9 +3653,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3855,7 +3661,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3873,13 +3678,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3902,9 +3700,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>M1</t>
@@ -3938,9 +3733,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>M2</t>
@@ -3974,9 +3766,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>M3</t>
@@ -4010,9 +3799,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>M4</t>
@@ -4046,9 +3832,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>M5</t>
@@ -4082,9 +3865,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>M6</t>
@@ -4118,9 +3898,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>M7</t>
@@ -4144,14 +3921,6 @@
           <t>CWL.EPCX2.5/4</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4174,9 +3943,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>N1</t>
@@ -4210,9 +3976,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>N2</t>
@@ -4246,9 +4009,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>N3</t>
@@ -4272,14 +4032,6 @@
           <t>CWL.EPCX2.5/4</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4302,9 +4054,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4313,7 +4062,6 @@
       <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4321,12 +4069,6 @@
           <t>1XT1</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>M</t>
@@ -4335,7 +4077,6 @@
       <c r="I50" t="n">
         <v>2</v>
       </c>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4358,9 +4099,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>1</t>
@@ -4369,7 +4107,6 @@
       <c r="I51" t="n">
         <v>1</v>
       </c>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4377,12 +4114,6 @@
           <t>1XT1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>2</t>
@@ -4391,7 +4122,6 @@
       <c r="I52" t="n">
         <v>2</v>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4409,13 +4139,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4438,9 +4161,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4449,7 +4169,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4467,13 +4186,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4496,9 +4208,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4507,7 +4216,6 @@
       <c r="I56" t="n">
         <v>1</v>
       </c>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4515,12 +4223,6 @@
           <t>1XT2</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>M</t>
@@ -4529,7 +4231,6 @@
       <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4552,9 +4253,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>1</t>
@@ -4563,7 +4261,6 @@
       <c r="I58" t="n">
         <v>1</v>
       </c>
-      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4571,12 +4268,6 @@
           <t>1XT2</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>2</t>
@@ -4585,7 +4276,6 @@
       <c r="I59" t="n">
         <v>2</v>
       </c>
-      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4608,9 +4298,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>3</t>
@@ -4619,7 +4306,6 @@
       <c r="I60" t="n">
         <v>1</v>
       </c>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4627,12 +4313,6 @@
           <t>1XT2</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>4</t>
@@ -4641,7 +4321,6 @@
       <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4659,13 +4338,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4688,9 +4360,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4699,7 +4368,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4717,13 +4385,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4746,9 +4407,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>1</t>
@@ -4757,7 +4415,6 @@
       <c r="I65" t="n">
         <v>1</v>
       </c>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4765,12 +4422,6 @@
           <t>1XT3</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>2</t>
@@ -4804,9 +4455,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>3</t>
@@ -4815,7 +4463,6 @@
       <c r="I67" t="n">
         <v>1</v>
       </c>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4823,12 +4470,6 @@
           <t>1XT3</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>4</t>
@@ -4862,9 +4503,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>5</t>
@@ -4873,7 +4511,6 @@
       <c r="I69" t="n">
         <v>1</v>
       </c>
-      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4881,12 +4518,6 @@
           <t>1XT3</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>6</t>
@@ -4895,7 +4526,6 @@
       <c r="I70" t="n">
         <v>2</v>
       </c>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4918,9 +4548,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>7</t>
@@ -4929,7 +4556,6 @@
       <c r="I71" t="n">
         <v>1</v>
       </c>
-      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4937,12 +4563,6 @@
           <t>1XT3</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>8</t>
@@ -4951,7 +4571,6 @@
       <c r="I72" t="n">
         <v>2</v>
       </c>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4969,13 +4588,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4998,9 +4610,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5009,7 +4618,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5027,13 +4635,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5056,9 +4657,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>L+</t>
@@ -5067,7 +4665,6 @@
       <c r="I76" t="n">
         <v>1</v>
       </c>
-      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5075,12 +4672,6 @@
           <t>1XT4</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>M</t>
@@ -5089,7 +4680,6 @@
       <c r="I77" t="n">
         <v>2</v>
       </c>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5112,9 +4702,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>1</t>
@@ -5123,7 +4710,6 @@
       <c r="I78" t="n">
         <v>1</v>
       </c>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5131,12 +4717,6 @@
           <t>1XT4</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>2</t>
@@ -5145,7 +4725,6 @@
       <c r="I79" t="n">
         <v>2</v>
       </c>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5168,9 +4747,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>3</t>
@@ -5179,7 +4755,6 @@
       <c r="I80" t="n">
         <v>1</v>
       </c>
-      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5187,12 +4762,6 @@
           <t>1XT4</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>4</t>
@@ -5201,7 +4770,6 @@
       <c r="I81" t="n">
         <v>2</v>
       </c>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5219,13 +4787,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5248,9 +4809,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5259,7 +4817,6 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5277,13 +4834,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5306,9 +4856,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>L+</t>
@@ -5317,7 +4864,6 @@
       <c r="I85" t="n">
         <v>1</v>
       </c>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5325,12 +4871,6 @@
           <t>2XT1</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>M</t>
@@ -5339,7 +4879,6 @@
       <c r="I86" t="n">
         <v>2</v>
       </c>
-      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5362,9 +4901,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>1</t>
@@ -5373,7 +4909,6 @@
       <c r="I87" t="n">
         <v>1</v>
       </c>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5381,12 +4916,6 @@
           <t>2XT1</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>2</t>
@@ -5395,7 +4924,6 @@
       <c r="I88" t="n">
         <v>2</v>
       </c>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5413,13 +4941,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5442,9 +4963,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5453,7 +4971,6 @@
       <c r="I90" t="n">
         <v>0</v>
       </c>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5471,13 +4988,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5500,9 +5010,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>L+</t>
@@ -5511,7 +5018,6 @@
       <c r="I92" t="n">
         <v>1</v>
       </c>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5519,12 +5025,6 @@
           <t>2XT2</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>M</t>
@@ -5533,7 +5033,6 @@
       <c r="I93" t="n">
         <v>2</v>
       </c>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5556,9 +5055,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>1</t>
@@ -5567,7 +5063,6 @@
       <c r="I94" t="n">
         <v>1</v>
       </c>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5575,12 +5070,6 @@
           <t>2XT2</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>2</t>
@@ -5589,7 +5078,6 @@
       <c r="I95" t="n">
         <v>2</v>
       </c>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5612,9 +5100,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>3</t>
@@ -5623,7 +5108,6 @@
       <c r="I96" t="n">
         <v>1</v>
       </c>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5631,12 +5115,6 @@
           <t>2XT2</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>4</t>
@@ -5645,7 +5123,6 @@
       <c r="I97" t="n">
         <v>2</v>
       </c>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5663,13 +5140,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5692,9 +5162,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5703,7 +5170,6 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5721,13 +5187,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5750,9 +5209,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>1</t>
@@ -5761,7 +5217,6 @@
       <c r="I101" t="n">
         <v>1</v>
       </c>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5769,12 +5224,6 @@
           <t>2XT3</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>2</t>
@@ -5808,9 +5257,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>3</t>
@@ -5819,7 +5265,6 @@
       <c r="I103" t="n">
         <v>1</v>
       </c>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5827,12 +5272,6 @@
           <t>2XT3</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>4</t>
@@ -5866,9 +5305,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>5</t>
@@ -5877,7 +5313,6 @@
       <c r="I105" t="n">
         <v>1</v>
       </c>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5885,12 +5320,6 @@
           <t>2XT3</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>6</t>
@@ -5899,7 +5328,6 @@
       <c r="I106" t="n">
         <v>2</v>
       </c>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5922,9 +5350,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>7</t>
@@ -5933,7 +5358,6 @@
       <c r="I107" t="n">
         <v>1</v>
       </c>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5941,12 +5365,6 @@
           <t>2XT3</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>8</t>
@@ -5955,7 +5373,6 @@
       <c r="I108" t="n">
         <v>2</v>
       </c>
-      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5973,13 +5390,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6002,9 +5412,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6013,7 +5420,6 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6031,13 +5437,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6060,9 +5459,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>L+</t>
@@ -6071,7 +5467,6 @@
       <c r="I112" t="n">
         <v>1</v>
       </c>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6079,12 +5474,6 @@
           <t>2XT4</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>M</t>
@@ -6093,7 +5482,6 @@
       <c r="I113" t="n">
         <v>2</v>
       </c>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6116,9 +5504,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>1</t>
@@ -6127,7 +5512,6 @@
       <c r="I114" t="n">
         <v>1</v>
       </c>
-      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6135,12 +5519,6 @@
           <t>2XT4</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>2</t>
@@ -6149,7 +5527,6 @@
       <c r="I115" t="n">
         <v>2</v>
       </c>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6172,9 +5549,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>3</t>
@@ -6183,7 +5557,6 @@
       <c r="I116" t="n">
         <v>1</v>
       </c>
-      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6191,12 +5564,6 @@
           <t>2XT4</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>4</t>
@@ -6205,7 +5572,6 @@
       <c r="I117" t="n">
         <v>2</v>
       </c>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6223,13 +5589,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6252,9 +5611,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6263,7 +5619,6 @@
       <c r="I119" t="n">
         <v>0</v>
       </c>
-      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6281,13 +5636,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6310,9 +5658,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>1</t>
@@ -6321,7 +5666,6 @@
       <c r="I121" t="n">
         <v>1</v>
       </c>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6329,12 +5673,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>2</t>
@@ -6368,9 +5706,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>3</t>
@@ -6379,7 +5714,6 @@
       <c r="I123" t="n">
         <v>1</v>
       </c>
-      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6387,12 +5721,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>4</t>
@@ -6426,9 +5754,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>5</t>
@@ -6437,7 +5762,6 @@
       <c r="I125" t="n">
         <v>1</v>
       </c>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6445,12 +5769,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>6</t>
@@ -6484,9 +5802,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>7</t>
@@ -6495,7 +5810,6 @@
       <c r="I127" t="n">
         <v>1</v>
       </c>
-      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6503,12 +5817,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>8</t>
@@ -6542,9 +5850,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>9</t>
@@ -6553,7 +5858,6 @@
       <c r="I129" t="n">
         <v>1</v>
       </c>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6561,12 +5865,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>10</t>
@@ -6575,7 +5873,6 @@
       <c r="I130" t="n">
         <v>2</v>
       </c>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6598,9 +5895,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>11</t>
@@ -6609,7 +5903,6 @@
       <c r="I131" t="n">
         <v>1</v>
       </c>
-      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6617,12 +5910,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>12</t>
@@ -6631,7 +5918,6 @@
       <c r="I132" t="n">
         <v>2</v>
       </c>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6654,9 +5940,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>13</t>
@@ -6665,7 +5948,6 @@
       <c r="I133" t="n">
         <v>1</v>
       </c>
-      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6673,12 +5955,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>14</t>
@@ -6712,9 +5988,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>15</t>
@@ -6723,7 +5996,6 @@
       <c r="I135" t="n">
         <v>1</v>
       </c>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6731,12 +6003,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>16</t>
@@ -6770,9 +6036,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>17</t>
@@ -6781,7 +6044,6 @@
       <c r="I137" t="n">
         <v>1</v>
       </c>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6789,12 +6051,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>18</t>
@@ -6828,9 +6084,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>19</t>
@@ -6839,7 +6092,6 @@
       <c r="I139" t="n">
         <v>1</v>
       </c>
-      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6847,12 +6099,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>20</t>
@@ -6861,7 +6107,6 @@
       <c r="I140" t="n">
         <v>2</v>
       </c>
-      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6884,9 +6129,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>21</t>
@@ -6895,7 +6137,6 @@
       <c r="I141" t="n">
         <v>1</v>
       </c>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6903,12 +6144,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>22</t>
@@ -6917,7 +6152,6 @@
       <c r="I142" t="n">
         <v>2</v>
       </c>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6940,9 +6174,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>23</t>
@@ -6951,7 +6182,6 @@
       <c r="I143" t="n">
         <v>1</v>
       </c>
-      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6959,12 +6189,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>24</t>
@@ -6998,9 +6222,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>25</t>
@@ -7009,7 +6230,6 @@
       <c r="I145" t="n">
         <v>1</v>
       </c>
-      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7017,12 +6237,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>26</t>
@@ -7056,9 +6270,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>27</t>
@@ -7067,7 +6278,6 @@
       <c r="I147" t="n">
         <v>1</v>
       </c>
-      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7075,12 +6285,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>28</t>
@@ -7114,9 +6318,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>29</t>
@@ -7125,7 +6326,6 @@
       <c r="I149" t="n">
         <v>1</v>
       </c>
-      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7133,12 +6333,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>30</t>
@@ -7172,9 +6366,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>31</t>
@@ -7183,7 +6374,6 @@
       <c r="I151" t="n">
         <v>1</v>
       </c>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7191,12 +6381,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>32</t>
@@ -7205,7 +6389,6 @@
       <c r="I152" t="n">
         <v>2</v>
       </c>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7228,9 +6411,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>33</t>
@@ -7239,7 +6419,6 @@
       <c r="I153" t="n">
         <v>1</v>
       </c>
-      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7247,12 +6426,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>34</t>
@@ -7261,7 +6434,6 @@
       <c r="I154" t="n">
         <v>2</v>
       </c>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7284,9 +6456,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>35</t>
@@ -7295,7 +6464,6 @@
       <c r="I155" t="n">
         <v>1</v>
       </c>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7303,12 +6471,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>36</t>
@@ -7342,9 +6504,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>37</t>
@@ -7353,7 +6512,6 @@
       <c r="I157" t="n">
         <v>1</v>
       </c>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7361,12 +6519,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>38</t>
@@ -7400,9 +6552,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>39</t>
@@ -7411,7 +6560,6 @@
       <c r="I159" t="n">
         <v>1</v>
       </c>
-      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7419,12 +6567,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>40</t>
@@ -7458,9 +6600,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>41</t>
@@ -7469,7 +6608,6 @@
       <c r="I161" t="n">
         <v>1</v>
       </c>
-      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7477,12 +6615,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>42</t>
@@ -7491,7 +6623,6 @@
       <c r="I162" t="n">
         <v>2</v>
       </c>
-      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7514,9 +6645,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>43</t>
@@ -7525,7 +6653,6 @@
       <c r="I163" t="n">
         <v>1</v>
       </c>
-      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7533,12 +6660,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>44</t>
@@ -7547,7 +6668,6 @@
       <c r="I164" t="n">
         <v>2</v>
       </c>
-      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7570,9 +6690,6 @@
           <t>1,5</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>45</t>
@@ -7581,7 +6698,6 @@
       <c r="I165" t="n">
         <v>1</v>
       </c>
-      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7589,12 +6705,6 @@
           <t>3XT1</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>46</t>
@@ -7603,7 +6713,6 @@
       <c r="I166" t="n">
         <v>2</v>
       </c>
-      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7621,13 +6730,6 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7650,9 +6752,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>PE</t>
@@ -7661,7 +6760,6 @@
       <c r="I168" t="n">
         <v>0</v>
       </c>
-      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7684,9 +6782,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>PE</t>
@@ -7695,7 +6790,6 @@
       <c r="I169" t="n">
         <v>0</v>
       </c>
-      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7718,9 +6812,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>PE</t>
@@ -7729,7 +6820,6 @@
       <c r="I170" t="n">
         <v>0</v>
       </c>
-      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7752,9 +6842,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>PE</t>
@@ -7763,7 +6850,6 @@
       <c r="I171" t="n">
         <v>0</v>
       </c>
-      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7781,13 +6867,6 @@
           <t>EPCX2.5</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7805,7 +6884,4094 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Модуль</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Стрелка слева</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Стрелка вправо</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Выходы NPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM5210808TN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Входы</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM5210808TN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Выходы</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/5.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-1QFU5:1 / 4.3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GL20-1600END</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Входы</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/5.2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-KBF1:24 / 7.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-2K1:13+ / 9.2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GL20-1600END</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Входы</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/5.2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-1K1:13+ / 8.3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GL20-0016ETP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Выходы</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>/5.2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-XM1:M5/4.8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GL20-0016ETP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Выходы</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>/5.2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-XM1:M5/4.8</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Модуль</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Назначение</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Элемент</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Обозначение</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Поток 1.
+Энкодер
+канал А</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPU-DI0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1XT1:1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Поток 1.
+Энкодер
+канал B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CPU-DI1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1XT1:2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Поток 2.
+Энкодер
+канал А</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CPU-DI2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2XT1:1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Поток 2.
+Энкодер
+канал B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CPU-DI3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2XT1:2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>БП - ОК</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CPU-DI4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-U1:DC OK</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ошибка ИБП</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CPU-DI5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-UPS:Input DC 24V:3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Режим работа
+от батареи</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CPU-DI6</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-UPS:Input DC 24V:4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Батарея
+заряжается</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CPU-DI7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-UPS:Input DC 24V:5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CPU.DI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COM IN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-XM1:M3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Колонна.
+Зеленый</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU-Q0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-K1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>/7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Колонна.
+Желтый</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CPU-Q1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-K2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>/7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Колонна.
+Красный</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CPU-Q2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-K3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>/7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Колонна.
+Зуммер</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CPU-Q3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-K4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>/7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CPU-Q4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-K5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>/16.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CPU-Q5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Отключение
+ИБП</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CPU-Q6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-K7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>/2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Подсветка
+кнопки
+квитирования</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CPU-Q7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Лампа</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-S1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>24V BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CPU.DO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COM OUT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-XM1:M3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Датчик камеры
+(1 поток)
+(опционально)
++ZM-1SO1:4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A1-DI0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1XT2:1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK1-XT2:2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A1-DI1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1XT2:2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK1-XT2:3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A1-DI2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1XT2:3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK1-XT2:4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A1-DI3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1XT2:4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Принтер1.
+Сигнал "Факт
+печати"</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A1-DI4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-1K1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>/15.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Принтер1.
+Сигнал
+"Интерлок"</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A1-DI5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-1K2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>/15.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A1-DI6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-1K3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>/12.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A1-DI7</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-1K4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>/12.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал
+готовности
+автомата
+Bosch1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A1-DI8</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-1K5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>/15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A1-DI9</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-1K6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>/15.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Сброс</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A1-DI10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-1K7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>/15.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Датчик метки
+от автомата
+Bosch1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A1-DI11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-1K8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>/15.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A1-DI12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-1K9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A1-DI13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-1K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COM IN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-XM1:M4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COM IN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-XM1:M4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Датчик камеры
+(2 поток)
+(опционально)
++ZM-1SO2:4</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A2-DI0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-2XT2:1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK2-XT2:2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>A2-DI1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-2XT2:2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK2-XT2:3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A2-DI2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-2XT2:3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Резерв
++1KK2-XT2:4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A2-DI3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-2XT2:4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Принтер2.
+Сигнал "Факт
+печати"</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A2-DI4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-2K1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>/16.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Принтер2.
+Сигнал
+"Интерлок"</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A2-DI5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-2K2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>/16.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A2-DI6</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-2K3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>/14.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A2-DI7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-2K4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>/14.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал
+готовности
+автомата
+Bosch2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>A2-DI8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-2K5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>/16.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A2-DI9</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-2K6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>/16.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Сброс</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A2-DI10</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Перекл</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-2K7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>/16.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Датчик метки
+от автомата
+Bosch2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>A2-DI11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-2K8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>/16.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A2-DI12</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-2K9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>A2-DI13</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ТТР</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-2K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Кнопка
+"Сброс
+ошибок"</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A2-DI14</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Кнопка НО</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Кнопка
+"Аварийный
+останов"</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>A2-DI15</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Кнопка НЗ</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-SB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>COM IN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-XM1:M4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>COM IN</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-XM1:M4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Триггер
+камеры
+поток1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A3-Q0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-1XT4:1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A3-Q1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-1XT4:2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>A3-Q2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-1XT4:3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>A3-Q3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-1XT4:4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>+24V</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1QFU4-1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Питание</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-1QFU4:1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал останова
+автомат Bosch1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>A3-Q8</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-1K11</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>/15.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал пинг
+WatchDog
+автомата Bosch1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>A3-Q9</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-1K12</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>/15.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Шкаф CPW.
+Подсветка кнопки
+"Режим настройки
+автомата" Bosch1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A3-Q10</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-1K13</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>/15.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>A3-Q11</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-1K14</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>/15.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>A3-Q12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-1K15</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>/15.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>COM OUT</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-XM1:M5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Триггер
+камеры
+поток2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>A4-Q0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-2XT4:1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>A4-Q1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-2XT4:2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>A4-Q2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-2XT4:3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>A4-Q3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-2XT4:4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>+24V</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1QFU4-1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Питание</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-1QFU4:1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал останова
+автомат Bosch2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>A4-Q8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-2K11</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>/16.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Шкаф CPW
+Сигнал пинг
+WatchDog
+автомата Bosch2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>A4-Q9</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-2K12</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>/16.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>A4-Q10</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-2K13</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>/16.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>A4-Q11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-2K14</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>/16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>A4-Q12</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Катушка</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-2K15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>/16.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>COM OUT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Общий</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-XM1:M5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ТТР,Перекл,Кнопка НО,Кнопка НЗ,Катушка,Лампа,Общий,Питание"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -7818,9 +10984,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -7888,6 +11052,98 @@
       <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">   «Общее количество клемм» считается автоматически: клеммы с заполненным «Поперечным сечением».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>СХЕМА Э3 (листы входов/выходов ПЛК)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Лист «Модули ПЛК»: одна строка — один модуль (CPU, A1 ...). Вид — «Входы» или «Выходы».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылка — где модуль изображён целиком (напр. /5.0), выводится под обозначением.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для входов: «Стрелка слева» — откуда приходит питание контактов реле и кнопок (напр. -KBF1:24 / 7.3), «Стрелка вправо» — куда питание уходит дальше; провод — марка/цвет/сечение этого провода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для выходов: «Стрелка слева» — общий провод катушек (напр. -XM1:M5/4.8); «Выходы NPN» = да, если модуль коммутирует минус (у катушки A2 — к выходу).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Лист «Каналы ПЛК»: одна строка — один вывод модуля, в порядке слева направо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Элемент (для входов): пусто — провод со стрелкой от «Связь»; ТТР — контакт твердотельного реле 13+/14; Перекл — перекидной контакт 11/14/12; Кнопка НО; Кнопка НЗ; Общий — COM модуля (стрелка вправо к «Связь»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Элемент (для выходов): пусто — провод стрелкой вниз к «Связь»; Катушка; Лампа; Общий — COM OUT (стрелка вправо); Питание — +24V модуля (приходит справа).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Обозначение — позиционное обозначение реле/кнопки (-2K1). Ссылки между катушками и контактами проставляются автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылка — вручную, если элемент на другом (не генерируемом) листе: у стрелки — лист.столбец цели (12.1), у контакта — где катушка (/16.3), у катушки — где контакт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Параметр — надпись у катушки/лампы (=24V).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Вывод без провода и элемента (резерв) рисуется только с подписью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   «Первый лист ПЛК в схеме» (лист «Проект»): если перед листами ПЛК в схеме должны идти другие листы (силовая часть и т.п.), укажите номер, с которого начинать — нумерация и ссылки будут с учётом этого.</t>
         </is>
       </c>
     </row>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клеммы" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модули ПЛК" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каналы ПЛК" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Питание 24В" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -600,23 +601,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Литера</t>
+          <t>Лист питания 24В в схеме</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Масса</t>
-        </is>
-      </c>
+          <t>Литера</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -694,6 +710,8 @@
           <t>Т.контр.</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -701,6 +719,8 @@
           <t>Нач.отд.</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -708,6 +728,8 @@
           <t>Н.контр.</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -804,6 +826,7 @@
           <t>INOVANCE</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -829,6 +852,7 @@
           <t>INOVANCE</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -854,6 +878,7 @@
           <t>INOVANCE</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -879,6 +904,7 @@
           <t>КИТ ЭНЕРГО</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -904,6 +930,7 @@
           <t>Klemsan</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -929,6 +956,7 @@
           <t>Klemsan</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -954,6 +982,7 @@
           <t>Klemsan</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -979,6 +1008,7 @@
           <t>Klemsan</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1004,6 +1034,7 @@
           <t>Klemsan</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1029,6 +1060,7 @@
           <t>STEZ</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1054,6 +1086,7 @@
           <t>Fortisflex</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1079,6 +1112,7 @@
           <t>Fortisflex</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1104,6 +1138,7 @@
           <t>Natclic</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1129,6 +1164,7 @@
           <t>Natclic</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1154,6 +1190,7 @@
           <t>Natclic</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1179,6 +1216,7 @@
           <t>MOXA</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1204,6 +1242,7 @@
           <t>MOXA</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1229,6 +1268,7 @@
           <t>Wiedmuller</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1254,6 +1294,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1279,6 +1320,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1304,6 +1346,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1329,6 +1372,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1354,6 +1398,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1379,6 +1424,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1404,6 +1450,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1429,6 +1476,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1454,6 +1502,7 @@
           <t>APT</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1479,6 +1528,7 @@
           <t>FINDER</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1504,6 +1554,7 @@
           <t>FINDER</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1529,6 +1580,7 @@
           <t>FINDER</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1554,6 +1606,7 @@
           <t>FINDER</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1579,6 +1632,7 @@
           <t>IFC</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1604,6 +1658,7 @@
           <t>IFC</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1629,6 +1684,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1654,6 +1710,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1679,6 +1736,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1704,6 +1762,7 @@
           <t>DEKraft</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1729,6 +1788,7 @@
           <t>DEKraft</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1754,6 +1814,7 @@
           <t>DEKraft</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1779,6 +1840,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1804,6 +1866,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1829,6 +1892,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1854,6 +1918,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1879,6 +1944,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1904,6 +1970,7 @@
           <t>Systeme Electric</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1929,6 +1996,7 @@
           <t>Natclic</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1954,6 +2022,7 @@
           <t>Wiedmuller</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1979,6 +2048,7 @@
           <t>Wiedmuller</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2004,6 +2074,7 @@
           <t>CABEUS</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2029,6 +2100,7 @@
           <t>CABEUS</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2054,6 +2126,7 @@
           <t>FLEXICORE</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2079,6 +2152,7 @@
           <t>ExeGate</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2104,6 +2178,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2129,6 +2204,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2154,6 +2230,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2179,6 +2256,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2204,6 +2282,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2229,6 +2308,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2254,6 +2334,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2279,6 +2360,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2304,6 +2386,7 @@
           <t>NIKOMAX</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2329,6 +2412,7 @@
           <t>CABEUS</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2354,6 +2438,7 @@
           <t>FUCON</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2379,6 +2464,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2404,6 +2490,7 @@
           <t>ConnectWell</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2429,6 +2516,7 @@
           <t>IEK</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2454,6 +2542,7 @@
           <t>CHINT</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2479,6 +2568,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2504,6 +2594,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2529,6 +2620,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2554,6 +2646,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2579,6 +2672,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2604,6 +2698,7 @@
           <t>Phoenix Contact</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2629,6 +2724,7 @@
           <t>FUCON</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2729,6 +2825,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>L1</t>
@@ -2737,6 +2836,7 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2759,6 +2859,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>L2</t>
@@ -2767,6 +2870,7 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2789,6 +2893,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>L3</t>
@@ -2797,6 +2904,7 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2819,6 +2927,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2827,6 +2938,7 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2849,6 +2961,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>PE</t>
@@ -2857,6 +2972,7 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2879,6 +2995,9 @@
           <t>6</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>PE</t>
@@ -2887,6 +3006,7 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2904,6 +3024,13 @@
           <t>EPCX4</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2926,6 +3053,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>L</t>
@@ -2934,6 +3064,7 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2956,6 +3087,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>N</t>
@@ -2964,6 +3098,7 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2986,6 +3121,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>PE</t>
@@ -2994,6 +3132,7 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3011,6 +3150,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3033,6 +3179,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>1</t>
@@ -3041,6 +3190,7 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3063,6 +3213,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>2</t>
@@ -3071,6 +3224,7 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3093,6 +3247,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>3</t>
@@ -3101,6 +3258,7 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3123,6 +3281,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>4</t>
@@ -3131,6 +3292,7 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3148,6 +3310,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3170,6 +3339,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>1L+</t>
@@ -3203,6 +3375,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>1L+</t>
@@ -3236,6 +3411,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>1M</t>
@@ -3269,6 +3447,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>1M</t>
@@ -3302,6 +3483,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>2L+</t>
@@ -3310,6 +3494,7 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3332,6 +3517,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>2M</t>
@@ -3340,6 +3528,7 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3357,6 +3546,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3379,6 +3575,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>L</t>
@@ -3387,6 +3586,7 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3409,6 +3609,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>N</t>
@@ -3417,6 +3620,7 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3439,6 +3643,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3447,6 +3654,7 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3464,6 +3672,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3486,6 +3701,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>L</t>
@@ -3494,6 +3712,7 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3516,6 +3735,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>N</t>
@@ -3524,6 +3746,7 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3546,6 +3769,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3554,6 +3780,7 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3571,6 +3798,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3593,6 +3827,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>L</t>
@@ -3601,6 +3838,7 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3623,6 +3861,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>N</t>
@@ -3631,6 +3872,7 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3653,6 +3895,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>PE</t>
@@ -3661,6 +3906,7 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3678,6 +3924,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3700,6 +3953,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>M1</t>
@@ -3733,6 +3989,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>M2</t>
@@ -3766,6 +4025,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>M3</t>
@@ -3799,6 +4061,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>M4</t>
@@ -3832,6 +4097,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>M5</t>
@@ -3865,6 +4133,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>M6</t>
@@ -3898,6 +4169,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>M7</t>
@@ -3921,6 +4195,14 @@
           <t>CWL.EPCX2.5/4</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3943,6 +4225,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>N1</t>
@@ -3976,6 +4261,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>N2</t>
@@ -4009,6 +4297,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>N3</t>
@@ -4032,6 +4323,14 @@
           <t>CWL.EPCX2.5/4</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4054,6 +4353,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4062,6 +4364,7 @@
       <c r="I49" t="n">
         <v>1</v>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4069,6 +4372,12 @@
           <t>1XT1</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>M</t>
@@ -4077,6 +4386,7 @@
       <c r="I50" t="n">
         <v>2</v>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4099,6 +4409,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>1</t>
@@ -4107,6 +4420,7 @@
       <c r="I51" t="n">
         <v>1</v>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4114,6 +4428,12 @@
           <t>1XT1</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>2</t>
@@ -4122,6 +4442,7 @@
       <c r="I52" t="n">
         <v>2</v>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4139,6 +4460,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4161,6 +4489,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4169,6 +4500,7 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4186,6 +4518,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4208,6 +4547,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4216,6 +4558,7 @@
       <c r="I56" t="n">
         <v>1</v>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4223,6 +4566,12 @@
           <t>1XT2</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>M</t>
@@ -4231,6 +4580,7 @@
       <c r="I57" t="n">
         <v>2</v>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4253,6 +4603,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>1</t>
@@ -4261,6 +4614,7 @@
       <c r="I58" t="n">
         <v>1</v>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4268,6 +4622,12 @@
           <t>1XT2</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>2</t>
@@ -4276,6 +4636,7 @@
       <c r="I59" t="n">
         <v>2</v>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4298,6 +4659,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>3</t>
@@ -4306,6 +4670,7 @@
       <c r="I60" t="n">
         <v>1</v>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4313,6 +4678,12 @@
           <t>1XT2</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>4</t>
@@ -4321,6 +4692,7 @@
       <c r="I61" t="n">
         <v>2</v>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4338,6 +4710,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4360,6 +4739,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4368,6 +4750,7 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4385,6 +4768,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4407,6 +4797,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>1</t>
@@ -4415,6 +4808,7 @@
       <c r="I65" t="n">
         <v>1</v>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4422,6 +4816,12 @@
           <t>1XT3</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>2</t>
@@ -4455,6 +4855,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>3</t>
@@ -4463,6 +4866,7 @@
       <c r="I67" t="n">
         <v>1</v>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4470,6 +4874,12 @@
           <t>1XT3</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>4</t>
@@ -4503,6 +4913,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>5</t>
@@ -4511,6 +4924,7 @@
       <c r="I69" t="n">
         <v>1</v>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4518,6 +4932,12 @@
           <t>1XT3</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>6</t>
@@ -4526,6 +4946,7 @@
       <c r="I70" t="n">
         <v>2</v>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4548,6 +4969,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>7</t>
@@ -4556,6 +4980,7 @@
       <c r="I71" t="n">
         <v>1</v>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4563,6 +4988,12 @@
           <t>1XT3</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>8</t>
@@ -4571,6 +5002,7 @@
       <c r="I72" t="n">
         <v>2</v>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4588,6 +5020,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4610,6 +5049,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4618,6 +5060,7 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4635,6 +5078,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4657,6 +5107,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4665,6 +5118,7 @@
       <c r="I76" t="n">
         <v>1</v>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4672,6 +5126,12 @@
           <t>1XT4</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>M</t>
@@ -4680,6 +5140,7 @@
       <c r="I77" t="n">
         <v>2</v>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4702,6 +5163,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>1</t>
@@ -4710,6 +5174,7 @@
       <c r="I78" t="n">
         <v>1</v>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4717,6 +5182,12 @@
           <t>1XT4</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>2</t>
@@ -4725,6 +5196,7 @@
       <c r="I79" t="n">
         <v>2</v>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4747,6 +5219,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>3</t>
@@ -4755,6 +5230,7 @@
       <c r="I80" t="n">
         <v>1</v>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4762,6 +5238,12 @@
           <t>1XT4</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>4</t>
@@ -4770,6 +5252,7 @@
       <c r="I81" t="n">
         <v>2</v>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4787,6 +5270,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4809,6 +5299,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4817,6 +5310,7 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4834,6 +5328,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4856,6 +5357,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>L+</t>
@@ -4864,6 +5368,7 @@
       <c r="I85" t="n">
         <v>1</v>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4871,6 +5376,12 @@
           <t>2XT1</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>M</t>
@@ -4879,6 +5390,7 @@
       <c r="I86" t="n">
         <v>2</v>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4901,6 +5413,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>1</t>
@@ -4909,6 +5424,7 @@
       <c r="I87" t="n">
         <v>1</v>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4916,6 +5432,12 @@
           <t>2XT1</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>2</t>
@@ -4924,6 +5446,7 @@
       <c r="I88" t="n">
         <v>2</v>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4941,6 +5464,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4963,6 +5493,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>PE</t>
@@ -4971,6 +5504,7 @@
       <c r="I90" t="n">
         <v>0</v>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4988,6 +5522,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5010,6 +5551,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>L+</t>
@@ -5018,6 +5562,7 @@
       <c r="I92" t="n">
         <v>1</v>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5025,6 +5570,12 @@
           <t>2XT2</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>M</t>
@@ -5033,6 +5584,7 @@
       <c r="I93" t="n">
         <v>2</v>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5055,6 +5607,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>1</t>
@@ -5063,6 +5618,7 @@
       <c r="I94" t="n">
         <v>1</v>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5070,6 +5626,12 @@
           <t>2XT2</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>2</t>
@@ -5078,6 +5640,7 @@
       <c r="I95" t="n">
         <v>2</v>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5100,6 +5663,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>3</t>
@@ -5108,6 +5674,7 @@
       <c r="I96" t="n">
         <v>1</v>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5115,6 +5682,12 @@
           <t>2XT2</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>4</t>
@@ -5123,6 +5696,7 @@
       <c r="I97" t="n">
         <v>2</v>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5140,6 +5714,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5162,6 +5743,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5170,6 +5754,7 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5187,6 +5772,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5209,6 +5801,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>1</t>
@@ -5217,6 +5812,7 @@
       <c r="I101" t="n">
         <v>1</v>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5224,6 +5820,12 @@
           <t>2XT3</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>2</t>
@@ -5257,6 +5859,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>3</t>
@@ -5265,6 +5870,7 @@
       <c r="I103" t="n">
         <v>1</v>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5272,6 +5878,12 @@
           <t>2XT3</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>4</t>
@@ -5305,6 +5917,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>5</t>
@@ -5313,6 +5928,7 @@
       <c r="I105" t="n">
         <v>1</v>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5320,6 +5936,12 @@
           <t>2XT3</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>6</t>
@@ -5328,6 +5950,7 @@
       <c r="I106" t="n">
         <v>2</v>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5350,6 +5973,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>7</t>
@@ -5358,6 +5984,7 @@
       <c r="I107" t="n">
         <v>1</v>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5365,6 +5992,12 @@
           <t>2XT3</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>8</t>
@@ -5373,6 +6006,7 @@
       <c r="I108" t="n">
         <v>2</v>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5390,6 +6024,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5412,6 +6053,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5420,6 +6064,7 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5437,6 +6082,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5459,6 +6111,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>L+</t>
@@ -5467,6 +6122,7 @@
       <c r="I112" t="n">
         <v>1</v>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5474,6 +6130,12 @@
           <t>2XT4</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>M</t>
@@ -5482,6 +6144,7 @@
       <c r="I113" t="n">
         <v>2</v>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5504,6 +6167,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>1</t>
@@ -5512,6 +6178,7 @@
       <c r="I114" t="n">
         <v>1</v>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5519,6 +6186,12 @@
           <t>2XT4</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>2</t>
@@ -5527,6 +6200,7 @@
       <c r="I115" t="n">
         <v>2</v>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5549,6 +6223,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>3</t>
@@ -5557,6 +6234,7 @@
       <c r="I116" t="n">
         <v>1</v>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5564,6 +6242,12 @@
           <t>2XT4</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>4</t>
@@ -5572,6 +6256,7 @@
       <c r="I117" t="n">
         <v>2</v>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5589,6 +6274,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5611,6 +6303,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>PE</t>
@@ -5619,6 +6314,7 @@
       <c r="I119" t="n">
         <v>0</v>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5636,6 +6332,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5658,6 +6361,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>1</t>
@@ -5666,6 +6372,7 @@
       <c r="I121" t="n">
         <v>1</v>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5673,6 +6380,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>2</t>
@@ -5706,6 +6419,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>3</t>
@@ -5714,6 +6430,7 @@
       <c r="I123" t="n">
         <v>1</v>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5721,6 +6438,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>4</t>
@@ -5754,6 +6477,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>5</t>
@@ -5762,6 +6488,7 @@
       <c r="I125" t="n">
         <v>1</v>
       </c>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5769,6 +6496,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>6</t>
@@ -5802,6 +6535,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>7</t>
@@ -5810,6 +6546,7 @@
       <c r="I127" t="n">
         <v>1</v>
       </c>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5817,6 +6554,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>8</t>
@@ -5850,6 +6593,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>9</t>
@@ -5858,6 +6604,7 @@
       <c r="I129" t="n">
         <v>1</v>
       </c>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5865,6 +6612,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>10</t>
@@ -5873,6 +6626,7 @@
       <c r="I130" t="n">
         <v>2</v>
       </c>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5895,6 +6649,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>11</t>
@@ -5903,6 +6660,7 @@
       <c r="I131" t="n">
         <v>1</v>
       </c>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5910,6 +6668,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>12</t>
@@ -5918,6 +6682,7 @@
       <c r="I132" t="n">
         <v>2</v>
       </c>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5940,6 +6705,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>13</t>
@@ -5948,6 +6716,7 @@
       <c r="I133" t="n">
         <v>1</v>
       </c>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5955,6 +6724,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>14</t>
@@ -5988,6 +6763,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>15</t>
@@ -5996,6 +6774,7 @@
       <c r="I135" t="n">
         <v>1</v>
       </c>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6003,6 +6782,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>16</t>
@@ -6036,6 +6821,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>17</t>
@@ -6044,6 +6832,7 @@
       <c r="I137" t="n">
         <v>1</v>
       </c>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6051,6 +6840,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>18</t>
@@ -6084,6 +6879,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>19</t>
@@ -6092,6 +6890,7 @@
       <c r="I139" t="n">
         <v>1</v>
       </c>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6099,6 +6898,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>20</t>
@@ -6107,6 +6912,7 @@
       <c r="I140" t="n">
         <v>2</v>
       </c>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6129,6 +6935,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>21</t>
@@ -6137,6 +6946,7 @@
       <c r="I141" t="n">
         <v>1</v>
       </c>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6144,6 +6954,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>22</t>
@@ -6152,6 +6968,7 @@
       <c r="I142" t="n">
         <v>2</v>
       </c>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6174,6 +6991,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>23</t>
@@ -6182,6 +7002,7 @@
       <c r="I143" t="n">
         <v>1</v>
       </c>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6189,6 +7010,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>24</t>
@@ -6222,6 +7049,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>25</t>
@@ -6230,6 +7060,7 @@
       <c r="I145" t="n">
         <v>1</v>
       </c>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6237,6 +7068,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>26</t>
@@ -6270,6 +7107,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>27</t>
@@ -6278,6 +7118,7 @@
       <c r="I147" t="n">
         <v>1</v>
       </c>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6285,6 +7126,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>28</t>
@@ -6318,6 +7165,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>29</t>
@@ -6326,6 +7176,7 @@
       <c r="I149" t="n">
         <v>1</v>
       </c>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6333,6 +7184,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>30</t>
@@ -6366,6 +7223,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>31</t>
@@ -6374,6 +7234,7 @@
       <c r="I151" t="n">
         <v>1</v>
       </c>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6381,6 +7242,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>32</t>
@@ -6389,6 +7256,7 @@
       <c r="I152" t="n">
         <v>2</v>
       </c>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6411,6 +7279,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>33</t>
@@ -6419,6 +7290,7 @@
       <c r="I153" t="n">
         <v>1</v>
       </c>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6426,6 +7298,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>34</t>
@@ -6434,6 +7312,7 @@
       <c r="I154" t="n">
         <v>2</v>
       </c>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6456,6 +7335,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>35</t>
@@ -6464,6 +7346,7 @@
       <c r="I155" t="n">
         <v>1</v>
       </c>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6471,6 +7354,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>36</t>
@@ -6504,6 +7393,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>37</t>
@@ -6512,6 +7404,7 @@
       <c r="I157" t="n">
         <v>1</v>
       </c>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6519,6 +7412,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>38</t>
@@ -6552,6 +7451,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>39</t>
@@ -6560,6 +7462,7 @@
       <c r="I159" t="n">
         <v>1</v>
       </c>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6567,6 +7470,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>40</t>
@@ -6600,6 +7509,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>41</t>
@@ -6608,6 +7520,7 @@
       <c r="I161" t="n">
         <v>1</v>
       </c>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6615,6 +7528,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>42</t>
@@ -6623,6 +7542,7 @@
       <c r="I162" t="n">
         <v>2</v>
       </c>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6645,6 +7565,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>43</t>
@@ -6653,6 +7576,7 @@
       <c r="I163" t="n">
         <v>1</v>
       </c>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6660,6 +7584,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>44</t>
@@ -6668,6 +7598,7 @@
       <c r="I164" t="n">
         <v>2</v>
       </c>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6690,6 +7621,9 @@
           <t>1,5</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>45</t>
@@ -6698,6 +7632,7 @@
       <c r="I165" t="n">
         <v>1</v>
       </c>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6705,6 +7640,12 @@
           <t>3XT1</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>46</t>
@@ -6713,6 +7654,7 @@
       <c r="I166" t="n">
         <v>2</v>
       </c>
+      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6730,6 +7672,13 @@
           <t>D-PTTBS 1,5/S</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6752,6 +7701,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6760,6 +7712,7 @@
       <c r="I168" t="n">
         <v>0</v>
       </c>
+      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6782,6 +7735,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6790,6 +7746,7 @@
       <c r="I169" t="n">
         <v>0</v>
       </c>
+      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6812,6 +7769,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6820,6 +7780,7 @@
       <c r="I170" t="n">
         <v>0</v>
       </c>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6842,6 +7803,9 @@
           <t>4</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>PE</t>
@@ -6850,6 +7814,7 @@
       <c r="I171" t="n">
         <v>0</v>
       </c>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6867,6 +7832,13 @@
           <t>EPCX2.5</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6983,6 +7955,12 @@
           <t>/5.0</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7015,6 +7993,7 @@
           <t>-1QFU5:1 / 4.3</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>1QFU5-1</t>
@@ -7042,6 +8021,7 @@
           <t>A1</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>GL20-1600END</t>
@@ -7082,6 +8062,7 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7089,6 +8070,7 @@
           <t>A2</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>GL20-1600END</t>
@@ -7109,6 +8091,7 @@
           <t>-1K1:13+ / 8.3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>1QFU5-1</t>
@@ -7124,6 +8107,7 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7131,6 +8115,7 @@
           <t>A3</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>GL20-0016ETP</t>
@@ -7151,6 +8136,7 @@
           <t>-XM1:M5/4.8</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>XM1-M5</t>
@@ -7166,6 +8152,7 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7173,6 +8160,7 @@
           <t>A4</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>GL20-0016ETP</t>
@@ -7193,6 +8181,7 @@
           <t>-XM1:M5/4.8</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>XM1-M5</t>
@@ -7208,6 +8197,7 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7326,6 +8316,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>-1XT1:1</t>
@@ -7336,6 +8328,7 @@
           <t>12.1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7370,6 +8363,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>-1XT1:2</t>
@@ -7380,6 +8375,7 @@
           <t>12.1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7414,6 +8410,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>-2XT1:1</t>
@@ -7424,6 +8422,7 @@
           <t>14.1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7458,6 +8457,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>-2XT1:2</t>
@@ -7468,6 +8469,7 @@
           <t>14.1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7500,6 +8502,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>-U1:DC OK</t>
@@ -7510,6 +8514,7 @@
           <t>2.6</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7542,6 +8547,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>-UPS:Input DC 24V:3</t>
@@ -7552,6 +8559,7 @@
           <t>2.8</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7585,6 +8593,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>-UPS:Input DC 24V:4</t>
@@ -7595,6 +8605,7 @@
           <t>2.8</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7628,6 +8639,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>-UPS:Input DC 24V:5</t>
@@ -7638,6 +8651,7 @@
           <t>2.8</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7675,6 +8689,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>-XM1:M3</t>
@@ -7685,6 +8700,7 @@
           <t>4.7</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7728,11 +8744,13 @@
           <t>-K1</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>/7.1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7776,11 +8794,13 @@
           <t>-K2</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>/7.2</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7824,11 +8844,13 @@
           <t>-K3</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>/7.2</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7872,11 +8894,13 @@
           <t>-K4</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>/7.3</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7919,11 +8943,13 @@
           <t>-K5</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>/16.8</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7966,6 +8992,9 @@
           <t>-K6</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8009,11 +9038,13 @@
           <t>-K7</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>/2.8</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8058,6 +9089,8 @@
           <t>-S1</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>24V BU</t>
@@ -8100,6 +9133,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>-XM1:M3</t>
@@ -8110,6 +9144,7 @@
           <t>4.7</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8145,6 +9180,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>-1XT2:1</t>
@@ -8155,6 +9192,7 @@
           <t>12.3</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8188,6 +9226,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>-1XT2:2</t>
@@ -8198,6 +9238,7 @@
           <t>12.3</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8231,6 +9272,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>-1XT2:3</t>
@@ -8241,6 +9284,7 @@
           <t>12.3</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8274,6 +9318,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>-1XT2:4</t>
@@ -8284,6 +9330,7 @@
           <t>12.4</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8328,11 +9375,13 @@
           <t>-1K1</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>/15.3</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8377,11 +9426,13 @@
           <t>-1K2</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>/15.4</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8424,11 +9475,13 @@
           <t>-1K3</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>/12.6</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8471,11 +9524,13 @@
           <t>-1K4</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>/12.7</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8522,11 +9577,13 @@
           <t>-1K5</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>/15.0</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8569,11 +9626,13 @@
           <t>-1K6</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>/15.1</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8616,11 +9675,13 @@
           <t>-1K7</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>/15.2</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8666,11 +9727,13 @@
           <t>-1K8</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>/15.3</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8713,6 +9776,9 @@
           <t>-1K9</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8755,6 +9821,9 @@
           <t>-1K10</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8772,6 +9841,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8789,6 +9866,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8826,6 +9911,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>-XM1:M4</t>
@@ -8836,6 +9922,7 @@
           <t>4.7</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8873,6 +9960,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>-XM1:M4</t>
@@ -8883,6 +9971,7 @@
           <t>4.7</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8918,6 +10007,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>-2XT2:1</t>
@@ -8928,6 +10019,7 @@
           <t>14.3</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8961,6 +10053,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>-2XT2:2</t>
@@ -8971,6 +10065,7 @@
           <t>14.3</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9004,6 +10099,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>-2XT2:3</t>
@@ -9014,6 +10111,7 @@
           <t>14.3</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9047,6 +10145,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>-2XT2:4</t>
@@ -9057,6 +10157,7 @@
           <t>14.4</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9101,11 +10202,13 @@
           <t>-2K1</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>/16.3</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9150,11 +10253,13 @@
           <t>-2K2</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>/16.4</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9197,11 +10302,13 @@
           <t>-2K3</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>/14.6</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9244,11 +10351,13 @@
           <t>-2K4</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>/14.7</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9295,11 +10404,13 @@
           <t>-2K5</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>/16.0</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9342,11 +10453,13 @@
           <t>-2K6</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>/16.1</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9389,11 +10502,13 @@
           <t>-2K7</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>/16.2</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9439,11 +10554,13 @@
           <t>-2K8</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>/16.3</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9486,6 +10603,9 @@
           <t>-2K9</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9528,6 +10648,9 @@
           <t>-2K10</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9572,6 +10695,9 @@
           <t>-S1</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9616,6 +10742,9 @@
           <t>-SB1</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9653,6 +10782,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>-XM1:M4</t>
@@ -9663,6 +10793,7 @@
           <t>4.8</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9700,6 +10831,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>-XM1:M4</t>
@@ -9710,6 +10842,7 @@
           <t>4.8</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9744,6 +10877,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>-1XT4:1</t>
@@ -9754,6 +10889,7 @@
           <t>12.8</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9786,6 +10922,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>-1XT4:2</t>
@@ -9796,6 +10934,7 @@
           <t>12.9</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9828,6 +10967,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>-1XT4:3</t>
@@ -9838,6 +10979,7 @@
           <t>12.9</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9870,6 +11012,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>-1XT4:4</t>
@@ -9880,6 +11024,7 @@
           <t>12.9</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9897,6 +11042,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9914,6 +11067,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9931,6 +11092,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9948,6 +11117,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9985,6 +11162,7 @@
           <t>Питание</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>-1QFU4:1</t>
@@ -9995,6 +11173,7 @@
           <t>4.2</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10039,11 +11218,13 @@
           <t>-1K11</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>/15.5</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10089,11 +11270,13 @@
           <t>-1K12</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>/15.5</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10139,11 +11322,13 @@
           <t>-1K13</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>/15.6</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10186,11 +11371,13 @@
           <t>-1K14</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>/15.7</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10233,11 +11420,13 @@
           <t>-1K15</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>/15.8</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10255,6 +11444,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10272,6 +11469,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10289,6 +11494,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10326,6 +11539,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>-XM1:M5</t>
@@ -10336,6 +11550,7 @@
           <t>4.8</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10370,6 +11585,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>-2XT4:1</t>
@@ -10380,6 +11597,7 @@
           <t>14.8</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10412,6 +11630,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>-2XT4:2</t>
@@ -10422,6 +11642,7 @@
           <t>14.9</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10454,6 +11675,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>-2XT4:3</t>
@@ -10464,6 +11687,7 @@
           <t>14.9</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10496,6 +11720,8 @@
           <t>0,5</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>-2XT4:4</t>
@@ -10506,6 +11732,7 @@
           <t>14.9</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10523,6 +11750,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10540,6 +11775,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10557,6 +11800,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10574,6 +11825,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10611,6 +11870,7 @@
           <t>Питание</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>-1QFU4:1</t>
@@ -10621,6 +11881,7 @@
           <t>4.2</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10665,11 +11926,13 @@
           <t>-2K11</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>/16.5</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10715,11 +11978,13 @@
           <t>-2K12</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>/16.5</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10732,6 +11997,7 @@
           <t>B3</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>A4-Q10</t>
@@ -10757,11 +12023,13 @@
           <t>-2K13</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>/16.6</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10804,11 +12072,13 @@
           <t>-2K14</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>/16.7</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10851,11 +12121,13 @@
           <t>-2K15</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>/16.8</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10873,6 +12145,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10890,6 +12170,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10907,6 +12195,14 @@
           <t>Резерв</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10944,6 +12240,7 @@
           <t>Общий</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>-XM1:M5</t>
@@ -10954,6 +12251,7 @@
           <t>4.8</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -10971,7 +12269,2172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Обозначение</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Номинал</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Связь 2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка 2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Подпись</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1L+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-X0.3:1L+</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-1QFU1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1QFU1-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-ES1:V+</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Питание коммутатора</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1QFU2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1QFU2-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-ES2:V+</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Питание коммутатора</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-1QFU3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1QFU3-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-CPU:+24V</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Питание ПЛК</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1QFU4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1QFU4-1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-A3:A9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-A4:A9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Питание I/O</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1QFU5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-U1:DC OK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-K1:A1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Питание диагностики</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1QFU6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DC 4A 'C'</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1QFU6-1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-PC1:XPS:+</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Питание ПромПК</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-1QFU7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DC 2A 'C'</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1QFU7-1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-OP1:+</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Питание монитора</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-1QFU8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Питание Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1QFU9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Питание Резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1L+</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-X0.3:1L+</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-2QFU1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2QFU1-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-1XT1:L+</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1 =24В энкодер</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-2QFU2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2QFU2-1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1XT2:L+</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1 =24В датчики</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-2QFU3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DC 4A 'C'</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2QFU3-1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-1XT4:L+</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1 =24В камеры</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-2QFU4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2QFU4-1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-2XT1:L+</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2 =24В энкодер</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-2QFU5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2QFU5-1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-2XT2:L+</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2 =24В датчик</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-2QFU6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DC 4A 'C'</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2QFU6-1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2XT4:L+</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2 =24В камеры</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-2QFU7</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Питание камеры (резерв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>автомат</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-2QFU8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DC 1A 'C'</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Питание резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-X0.3:1M</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>XM1-M1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-H2:X2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>XM1-M1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-ES2:V-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>XM1-M1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-KBF1:A2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-ES1:V-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-PC1:XPS:-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-OP1:DC:-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-CPU:0V</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-CPU:B9</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-CPU:A9</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-HL1:0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-S1:x1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-A1:B9</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-A1:A9</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-A2:B9</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>XM1-M4</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-A2:A9</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-A3:B9</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-1K11:A2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-A4:B9</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>XM1-M5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-2K11:A2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-1XT2:M</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-1XT1:M</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-2XT1:M</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-1XT4:M</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>отвод вверх</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>XM1-M7</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-2XT4:M</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>XM1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>отвод вниз</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>XM1-M7</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-2XT2:M</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ввод,автомат,отвод вверх,отвод вниз"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -10984,7 +14447,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -11055,7 +14520,9 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -11141,7 +14608,38 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ПИТАНИЕ 24 В (лист «Питание 24В»): строки по группам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Группа автоматов (напр. 1): строка «ввод» — откуда питание шины (Связь, провод); строки «автомат» — Обозначение (1QFU1), Номинал (DC 1A 'C'), провод, Связь/Ссылка — куда идёт (напр. -ES1:V+), Связь 2 — второй потребитель, Подпись — надпись в рамке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Шина минусов (Группа = имя клеммника, напр. XM1): «ввод» и строки «отвод вверх» / «отвод вниз» — Обозначение = клемма (M1), провод, Связь (-ES1:V-).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылки лист.столбец на стрелках можно не писать — если потребитель есть на листах ПЛК, ссылка подставится сама.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t xml:space="preserve">   «Первый лист ПЛК в схеме» (лист «Проект»): если перед листами ПЛК в схеме должны идти другие листы (силовая часть и т.п.), укажите номер, с которого начинать — нумерация и ссылки будут с учётом этого.</t>
         </is>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модули ПЛК" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каналы ПЛК" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Питание 24В" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Линии 230В" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -613,15 +614,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Литера</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>Лист линий 230В в схеме</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Литера</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -629,10 +634,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14434,7 +14447,433 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Автомат</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Номинал</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Утечка</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Питание L</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка L</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Питание N</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка N</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Клеммник</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Кабель</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Марка кабеля</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Жилы</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Розетки</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Номинал розеток</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка L</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка N</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка PE</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка нагрузки</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Подпись</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-QF1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>АВДТ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20A 'C'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30мА</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-QS1:8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-XN:N1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>W1LR1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H-нг(A)-HF</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3G2,5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1XS1;1XS2;1XS3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>16 A</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Питание лазера, дымоудаления и чиллера (поток 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>-QF2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>АВДТ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20A 'C'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30мА</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-QS1:6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-XN:N1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>W1LR2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H-нг(A)-HF</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3G2,5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1XS4;1XS5;1XS6</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>16 A</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Питание лазера, дымоудаления и чиллера (поток 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>-QF3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20A 'C'</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-SF4:1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-XN:N3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>WPW-TK1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H-нг(A)-HF</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3G2,5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>+CP1-X0:L1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>+CP1-X0:N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>+CP1-X0:PE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>+CP1/2.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Питание ТК</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"АВДТ,АВ"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -14639,7 +15078,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ЛИНИИ 230 В (лист «Линии 230В»): строка — отходящая линия: Автомат (QF1), Тип (АВДТ или АВ), Номинал (20A 'C'), Утечка (30мА), Сечение, Питание L (-QS1:8) и N (-XN:N1), Клеммник (X1), Кабель (W1LR1), Марка кабеля, Жилы (3G2,5), Зона (+ZM), Розетки (1XS1;1XS2;1XS3) или Нагрузка L/N/PE (стрелки), Подпись. Марки проводов (QF1-1, QF1-N1, QF1-2, QF1-N2) ставятся сами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t xml:space="preserve">   «Первый лист ПЛК в схеме» (лист «Проект»): если перед листами ПЛК в схеме должны идти другие листы (силовая часть и т.п.), укажите номер, с которого начинать — нумерация и ссылки будут с учётом этого.</t>
         </is>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каналы ПЛК" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Питание 24В" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Линии 230В" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ввод 230В" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -626,15 +627,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Литера</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>Лист ввода 230В в схеме</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Литера</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -642,10 +647,295 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>КАК ЗАПОЛНЯТЬ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Лист «Проект»: заполните колонку «Значение». Обязателен только «Шифр» (напр. ВКС.АСПУ.2196.СС1). К шифру добавляется суффикс спецификации (В4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Лист «Подписи»: фамилии и даты для основной надписи титульного листа (дату можно писать текстом «03.26»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Лист «Спецификация»: одна строка — одна позиция. № п/п проставляется автоматически. Длинные наименования переносятся сами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Лист «Клеммы»: одна строка — одна строка клеммного плана, в том же порядке, как на чертеже.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Клеммник — имя (X0, 1XT1 ...). Можно указать только в первой строке клеммника, ниже оставить пустым.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Метка — надпись клеммы справа (L1, PE, 1 ...). Пусто — для крышек и концевых пластин.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ярус — 0 (одноярусная, по умолчанию, если есть метка), 1 и 2 — верхний/нижний ярус двухъярусной клеммы, «-» — без риски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для второго яруса двухъярусной клеммы добавьте строку, где заполнены только Метка и Ярус=2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Группа перемычки — одинаковый номер у клемм, соединённых перемычкой (внутри одного клеммника).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   «Общее количество клемм» считается автоматически: клеммы с заполненным «Поперечным сечением».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>СХЕМА Э3 (листы входов/выходов ПЛК)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Лист «Модули ПЛК»: одна строка — один модуль (CPU, A1 ...). Вид — «Входы» или «Выходы».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылка — где модуль изображён целиком (напр. /5.0), выводится под обозначением.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для входов: «Стрелка слева» — откуда приходит питание контактов реле и кнопок (напр. -KBF1:24 / 7.3), «Стрелка вправо» — куда питание уходит дальше; провод — марка/цвет/сечение этого провода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для выходов: «Стрелка слева» — общий провод катушек (напр. -XM1:M5/4.8); «Выходы NPN» = да, если модуль коммутирует минус (у катушки A2 — к выходу).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Лист «Каналы ПЛК»: одна строка — один вывод модуля, в порядке слева направо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Элемент (для входов): пусто — провод со стрелкой от «Связь»; ТТР — контакт твердотельного реле 13+/14; Перекл — перекидной контакт 11/14/12; Кнопка НО; Кнопка НЗ; Общий — COM модуля (стрелка вправо к «Связь»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Элемент (для выходов): пусто — провод стрелкой вниз к «Связь»; Катушка; Лампа; Общий — COM OUT (стрелка вправо); Питание — +24V модуля (приходит справа).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Обозначение — позиционное обозначение реле/кнопки (-2K1). Ссылки между катушками и контактами проставляются автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылка — вручную, если элемент на другом (не генерируемом) листе: у стрелки — лист.столбец цели (12.1), у контакта — где катушка (/16.3), у катушки — где контакт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Параметр — надпись у катушки/лампы (=24V).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Вывод без провода и элемента (резерв) рисуется только с подписью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ПИТАНИЕ 24 В (лист «Питание 24В»): строки по группам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Группа автоматов (напр. 1): строка «ввод» — откуда питание шины (Связь, провод); строки «автомат» — Обозначение (1QFU1), Номинал (DC 1A 'C'), провод, Связь/Ссылка — куда идёт (напр. -ES1:V+), Связь 2 — второй потребитель, Подпись — надпись в рамке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Шина минусов (Группа = имя клеммника, напр. XM1): «ввод» и строки «отвод вверх» / «отвод вниз» — Обозначение = клемма (M1), провод, Связь (-ES1:V-).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ссылки лист.столбец на стрелках можно не писать — если потребитель есть на листах ПЛК, ссылка подставится сама.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ЛИНИИ 230 В (лист «Линии 230В»): строка — отходящая линия: Автомат (QF1), Тип (АВДТ или АВ), Номинал (20A 'C'), Утечка (30мА), Сечение, Питание L (-QS1:8) и N (-XN:N1), Клеммник (X1), Кабель (W1LR1), Марка кабеля, Жилы (3G2,5), Зона (+ZM), Розетки (1XS1;1XS2;1XS3) или Нагрузка L/N/PE (стрелки), Подпись. Марки проводов (QF1-1, QF1-N1, QF1-2, QF1-N2) ставятся сами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ВВОД 230 В (лист «Ввод 230В»): Тип строки —</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ввод — Обозначение клеммника (X0), Вывод — клеммы через пробел (L1 L2 L3 N PE), Название — кабель (W1E-001), Номинал — марка кабеля, Связь — откуда (-ШР);</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   выключатель — QS1, Номинал (40A), Вывод — число полюсов;</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   выход — полюс QS (2, 4 …), Связь: «шина» (общая шина автоматов), «N» или точка (-QF1:1); нейтраль — имя шины (XN); отвод n — клемма (N1), Связь (-QF1:N1);</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ветвь — автомат от шины (SF1, 6A 'C') и Нагрузка: розетка / лампа / термостат (+ вентилятор в «Нагрузка 2») / светильник / устройство / стрелка (Связь); Нейтраль — откуда N нагрузки (-XN:N2);</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   устройство — блок с выводами (U1, UPS): Название, Номинал; строки «вывод» — Обозначение устройства, Вывод (L, V+, 11), Сверху да/нет, провод, Связь. Устройство с тем же обозначением, что нагрузка ветви, рисуется в ветви.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   «Первый лист ПЛК в схеме» (лист «Проект»): если перед листами ПЛК в схеме должны идти другие листы (силовая часть и т.п.), укажите номер, с которого начинать — нумерация и ссылки будут с учётом этого.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14873,228 +15163,1991 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>КАК ЗАПОЛНЯТЬ</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Обозначение</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Номинал</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Сверху</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка обозн.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка парам.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка 2 обозн.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Нагрузка 2 парам.</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Нейтраль</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H-нг(A)-HF 5G2,5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>W1E-001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>L1 L2 L3 N PE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-ШР</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Лист «Проект»: заполните колонку «Значение». Обязателен только «Шифр» (напр. ВКС.АСПУ.2196.СС1). К шифру добавляется суффикс спецификации (В4).</t>
-        </is>
-      </c>
+          <t>выключатель</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QS1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>40A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Лист «Подписи»: фамилии и даты для основной надписи титульного листа (дату можно писать текстом «03.26»).</t>
-        </is>
-      </c>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>QS1-2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>шина</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Лист «Спецификация»: одна строка — одна позиция. № п/п проставляется автоматически. Длинные наименования переносятся сами.</t>
-        </is>
-      </c>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>QS1-4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-H1:X1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Лист «Клеммы»: одна строка — одна строка клеммного плана, в том же порядке, как на чертеже.</t>
-        </is>
-      </c>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>QF2-1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-QF2:1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Клеммник — имя (X0, 1XT1 ...). Можно указать только в первой строке клеммника, ниже оставить пустым.</t>
-        </is>
-      </c>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>QF1-1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-QF1:1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Метка — надпись клеммы справа (L1, PE, 1 ...). Пусто — для крышек и концевых пластин.</t>
-        </is>
-      </c>
+          <t>нейтраль</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>XN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ярус — 0 (одноярусная, по умолчанию, если есть метка), 1 и 2 — верхний/нижний ярус двухъярусной клеммы, «-» — без риски.</t>
-        </is>
-      </c>
+          <t>отвод n</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>QF1-N1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-QF1:N1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Для второго яруса двухъярусной клеммы добавьте строку, где заполнены только Метка и Ярус=2.</t>
-        </is>
-      </c>
+          <t>отвод n</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>QF2-N1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-QF2:N1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Группа перемычки — одинаковый номер у клемм, соединённых перемычкой (внутри одного клеммника).</t>
-        </is>
-      </c>
+          <t>отвод n</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X3-N</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-X3:N</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   «Общее количество клемм» считается автоматически: клеммы с заполненным «Поперечным сечением».</t>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-SF1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6A 'C'</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>розетка</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-XS1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16 A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SF1-2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>-XN:N2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-SF2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4A 'C'</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>термостат</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-TR1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-10..+80°C</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-EC1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>100м3/ч, 230VAC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SF2-2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>-XN:N2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>СХЕМА Э3 (листы входов/выходов ПЛК)</t>
-        </is>
-      </c>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-SF3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6A 'C'</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SF3-2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Лист «Модули ПЛК»: одна строка — один модуль (CPU, A1 ...). Вид — «Входы» или «Выходы».</t>
-        </is>
-      </c>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10 A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weidmüller PRO MAX 24V DC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ссылка — где модуль изображён целиком (напр. /5.0), выводится под обозначением.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Для входов: «Стрелка слева» — откуда приходит питание контактов реле и кнопок (напр. -KBF1:24 / 7.3), «Стрелка вправо» — куда питание уходит дальше; провод — марка/цвет/сечение этого провода.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>U1-N</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-XN:N2</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Для выходов: «Стрелка слева» — общий провод катушек (напр. -XM1:M5/4.8); «Выходы NPN» = да, если модуль коммутирует минус (у катушки A2 — к выходу).</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GNYE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-XPE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Лист «Каналы ПЛК»: одна строка — один вывод модуля, в порядке слева направо.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>V+</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>U1-V+</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-X0.3:2L+</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Элемент (для входов): пусто — провод со стрелкой от «Связь»; ТТР — контакт твердотельного реле 13+/14; Перекл — перекидной контакт 11/14/12; Кнопка НО; Кнопка НЗ; Общий — COM модуля (стрелка вправо к «Связь»).</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>V-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>U1-V-</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-X0.3:2M</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Элемент (для выходов): пусто — провод стрелкой вниз к «Связь»; Катушка; Лампа; Общий — COM OUT (стрелка вправо); Питание — +24V модуля (приходит справа).</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-U1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DC OK</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CPU-DI4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-CPU:A5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Обозначение — позиционное обозначение реле/кнопки (-2K1). Ссылки между катушками и контактами проставляются автоматически.</t>
-        </is>
-      </c>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-QF4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6A 'C'</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>стрелка</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>QF4-2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-X0.2:3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ссылка — вручную, если элемент на другом (не генерируемом) листе: у стрелки — лист.столбец цели (12.1), у контакта — где катушка (/16.3), у катушки — где контакт.</t>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-SF4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4A 'C'</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>светильник</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-EA1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5 Вт</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SF4-2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-XN:N3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Параметр — надпись у катушки/лампы (=24V).</t>
-        </is>
-      </c>
+          <t>ветвь</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>стрелка</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-QF3:1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Вывод без провода и элемента (резерв) рисуется только с подписью.</t>
-        </is>
-      </c>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10 A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CP DC UPS 24V 20A/10A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>U1-V+</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-U1:V+</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ПИТАНИЕ 24 В (лист «Питание 24В»): строки по группам.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>U1-V-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>-U1:V-</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Группа автоматов (напр. 1): строка «ввод» — откуда питание шины (Связь, провод); строки «автомат» — Обозначение (1QFU1), Номинал (DC 1A 'C'), провод, Связь/Ссылка — куда идёт (напр. -ES1:V+), Связь 2 — второй потребитель, Подпись — надпись в рамке.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-1QFU5:1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Шина минусов (Группа = имя клеммника, напр. XM1): «ввод» и строки «отвод вверх» / «отвод вниз» — Обозначение = клемма (M1), провод, Связь (-ES1:V-).</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>UPS-12</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-H2:X1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ссылки лист.столбец на стрелках можно не писать — если потребитель есть на листах ПЛК, ссылка подставится сама.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>UPS-24</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-KBF1:A1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CPU-DI5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-CPU:A6</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ЛИНИИ 230 В (лист «Линии 230В»): строка — отходящая линия: Автомат (QF1), Тип (АВДТ или АВ), Номинал (20A 'C'), Утечка (30мА), Сечение, Питание L (-QS1:8) и N (-XN:N1), Клеммник (X1), Кабель (W1LR1), Марка кабеля, Жилы (3G2,5), Зона (+ZM), Розетки (1XS1;1XS2;1XS3) или Нагрузка L/N/PE (стрелки), Подпись. Марки проводов (QF1-1, QF1-N1, QF1-2, QF1-N2) ставятся сами.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CPU-DI6</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-CPU:A7</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   «Первый лист ПЛК в схеме» (лист «Проект»): если перед листами ПЛК в схеме должны идти другие листы (силовая часть и т.п.), укажите номер, с которого начинать — нумерация и ссылки будут с учётом этого.</t>
-        </is>
-      </c>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>CPU-DI7</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-CPU:A8</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-X0.3:1L+</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>-X0.3:1M</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bat+</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>UPS-+</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>-GB1:4</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-UPS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bat-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>UPS-M</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>-GB1:3</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>-GB1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3,4 Ah</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Батарея 24V</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-GB1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-GB1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-GB1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>вывод</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-GB1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ввод,выключатель,выход,нейтраль,отвод n,ветвь,устройство,вывод"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"розетка,лампа,термостат,светильник,устройство,стрелка"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Natclic</t>
+          <t>Natсlic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Natclic</t>
+          <t>Natсlic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Natclic</t>
+          <t>Natсlic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Natclic</t>
+          <t>Natсlic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -2907,7 +2907,8 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Соединительные клеммы AKG 4 GNYE, тип подключения Винтовые зажимы, Ток нагрузки: 41 A, cечение: 0,5 мм² - 6 мм², ширина: 7 мм, Цвет: желто-зел.</t>
+          <t>Соединительные клеммы AKG 4 GNYE, тип подключения Винтовые зажимы, Ток
+нагрузки: 41 A, cечение: 0,5 мм² - 6 мм², ширина: 7 мм, Цвет: желто-зел.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4243,7 +4244,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4279,7 +4280,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4315,7 +4316,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4351,7 +4352,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4387,7 +4388,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4423,7 +4424,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4459,7 +4460,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4515,7 +4516,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4551,7 +4552,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4587,7 +4588,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CWL.CP2.5/4BU</t>
+          <t>CWl.CP2.5/4BU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Питание 24В" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Линии 230В" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ввод 230В" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,6 +672,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Лист схемы</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Страница образца</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Файл образца</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Разделы</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Отпечаток</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>mains</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ddb0ce8b2f6d756e5694f8eb1cc0a6a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>feeders</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32115411d02468c47ad5c438ff0a6db6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>power24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>abe81d144a08db09c37b4ec24324c27d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>plc:CPU.DI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6927d804b312035e06b59c795d67885a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>plc:CPU.DO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>e8c79e456e4d12a298f91f17f6b50bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2196_SS1.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -16,8 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Питание 24В" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Линии 230В" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ввод 230В" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сеть" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабели сети" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -640,15 +642,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Литера</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Лист сети в схеме</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Литера</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -656,10 +662,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -667,6 +681,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Устройство</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Сторона</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EDS-208</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>moxa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V+</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-1QFU2:1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1QFU2-1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-XM1:M1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>XM1-M1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-ES2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IFC-BOX-NS71-i7-12700T-32-1000-FAN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USB3.0 1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>usb</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USB3.0 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>usb</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LAN A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HDMI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>hdmi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USB2.0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>usb2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LAN B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-1QFU6:1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1QFU6-1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-PC1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-XM1:M2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-ES1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NAT-102</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>moxa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-ES1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-ES1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>rj45</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-ES1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>V+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-1QFU1:1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1QFU1-1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-ES1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>V-</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-XM1:M2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AM5210808TN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>inovance</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>/6.1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LAN A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EtherCAT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>+24V</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-1QFU3:1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1QFU3-1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0V</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-XM1:M2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>модуль</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A1 GL20-1600END /8.0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>модуль</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A2 GL20-1600END /9.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>модуль</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A3 GL20-0016ETP /10.0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>модуль</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-CPU</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A4 GL20-0016ETP /11.0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>устройство</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>-OP1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IFC-MW217C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ifc</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-OP1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HDMI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>hdmi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>порт</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-OP1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USB2.0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>usb2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-OP1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-1QFU7:1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1QFU7-1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-OP1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-XM1:M2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>XM1-M2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Кабель</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Откуда</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Куда</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Разъём</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Вид разъёма</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Удалённый конец</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Кабель дальше</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Марка дальше</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Устройство</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Название устройства</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Порт устройства</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-ES2:1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>XETH1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>+1KK1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>+1KK1-XETH1:RJ45</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>+1KK1/3.1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WET-1CM1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-ES2:2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>XETH2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>+1KK2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+1KK2-XETH1:RJ45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>+1KK2/3.1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>WET-1CM2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-ES2:3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>XETH3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>+CP1-XETH5:RJ45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>+CP1/5.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>WET-TK1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-ES2:4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>XETH4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>WET-1PR1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-1PR1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Принтер</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-ES2:5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>XETH5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>WET-1PR2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-1PR2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Принтер</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-ES2:6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>XETH6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-ES2:7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-CPU:LAN A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-ES2:8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-PC1:LAN A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-ES1:1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-PC1:LAN B</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>W010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-ES1:2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>XETH0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>WET-SR1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>-OMS</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Сервер</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>W011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S/FTP, CAT6A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-CPU:EtherCAT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>XECT1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>+CP1-XECT1:RJ45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>+CP1/5.1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>WETC-TK1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>F/UTP CAT6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WUSB1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USB 3.0 (A-A)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1,8 м</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-PC1:USB3.0 1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>XUSB1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>USB A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WUSB2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USB 3.0 (A-A)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1,8 м</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-PC1:USB3.0 2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>XUSB2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>USB A</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-1Scan1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ручной сканер\nQBT2500</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WOP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HDMI-HDMI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1,8 м</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-PC1:HDMI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-OP1:HDMI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>*входит в\nпоставку\nмонитора</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WTCH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>USBA-RJ-45(2.0)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1,8 м</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-PC1:USB2.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-OP1:USB2.0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>*входит в\nпоставку\nмонитора</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -790,8 +3206,16 @@
           <t>2196_SS1.pdf</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>024d0c3aad4f3b4c85e4d62a34eac76f</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -904,7 +3328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -18,8 +18,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ввод 230В" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сеть" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабели сети" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Коробки" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -654,15 +655,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Литера</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>Первый лист коробок в схеме</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Литера</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -670,10 +675,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Масштаб</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3088,6 +3101,6122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Y93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Клеммник</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Кабель</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка кабеля</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Марка кабеля</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Экран</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Парами</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Удалённое устройство</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Клемма</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Жила</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Удалённый конец</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка конца</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Элемент</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Обозначение</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Подпись</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Перемычка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>+1KK1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1XT1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WIO-1ENC1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+1KK1/2.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>+1KK1-XT1:L+</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>+1KK1/2.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2QFU1-1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-2QFU1:1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1XT1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>+1KK1-XT1:M</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>+1KK1/2.1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-XM1:M6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1XT1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>+1KK1-XT1:1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>+1KK1/2.1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CPU-DI0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-CPU:A1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Энкодер А</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1XT1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>+1KK1-XT1:2</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>+1KK1/2.1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CPU-DI1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-CPU:A2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Энкодер B</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WIO-1SO1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+1KK1/2.3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:+</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>+1KK1/2.3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2QFU2-1</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-2QFU2:1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:M</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>+1KK1/2.3</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-XM1:M6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>+1KK1/2.3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A1-DI0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-A1:A1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Датчик камеры</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>+1KK1/2.4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A1-DI1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-A1:A2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>+1KK1/2.4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A1-DI2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-A1:A3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1XT2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>+1KK1-XT2:4</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>+1KK1/2.5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A1-DI3</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-A1:A4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1K3-A1</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>-1K3</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1K3-A2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1K4-A1</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-1K4</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1XT3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1K4-A2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WIO-1CAM1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+1KK1/3.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:L+</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>+1KK1/3.1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2QFU3-1</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-2QFU3:1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:M</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>+1KK1/3.1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-XM1:M6</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>+1KK1/3.2</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A3-Q0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-A3:A1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Коробка 1КК1\nТриггер камеры</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:3</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>+1KK1/3.4</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A3-Q1</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-A3:A2</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>+1KK1/3.6</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A3-Q2</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-A3:A3</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1XT4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>+1KK1-XT4:7</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>+1KK1/3.8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A3-Q3</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-A3:A4</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>+1KK2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2XT1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WIO-1ENC2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+1KK2/2.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>+1KK2-XT1:L+</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>+1KK2/2.0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2QFU4-1</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-2QFU4:1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2XT1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>+1KK2-XT1:M</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>+1KK2/2.1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>XM1-M6</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-XM1:M6</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2XT1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>+1KK2-XT1:1</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>+1KK2/2.1</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CPU-DI2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-CPU:A3</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Энкодер А</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2XT1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>+1KK2-XT1:2</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>+1KK2/2.1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CPU-DI3</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-CPU:A4</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Энкодер B</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>WIO-1SO2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+1KK2/2.3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:+</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>+1KK2/2.3</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2QFU5-1</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-2QFU5:1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:M</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>+1KK2/2.3</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>XM1-M7</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-XM1:M7</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:1</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>+1KK2/2.3</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A2-DI0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-A2:A1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Датчик камеры</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:2</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>+1KK2/2.4</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A2-DI1</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-A2:A2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:3</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>+1KK2/2.4</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A2-DI2</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>-A2:A3</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2XT2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>+1KK2-XT2:4</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>+1KK2/2.5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A2-DI3</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>-A2:A4</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2K3-A1</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-2K3</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2K3-A2</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2K4-A1</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>-2K4</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2XT3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2K4-A2</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>WIO-1CAM2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>+1KK2/3.1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FLEXICORE 135 CH нг(A)-HF 7G0,75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>L+</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:L+</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>+1KK2/3.1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2QFU6-1</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>-2QFU6:1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:M</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>+1KK2/3.1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>XM1-M7</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>-XM1:M7</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>+1KK2/3.2</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A4-Q0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>-A4:A1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Коробка 1КК2\nТриггер камеры</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:3</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>+1KK2/3.4</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A4-Q1</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>-A4:A2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:5</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>+1KK2/3.6</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A4-Q2</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>-A4:A3</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2XT4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>+1KK2-XT4:7</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>+1KK2/3.8</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A4-Q3</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>-A4:A4</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>W1CPW1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H нг(A)-HF 10G0,75</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-CC_CPW</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1K5-A1</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>-1K5</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nСигнал готовности\nавтомата Bosch1</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0V</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1K5-A2</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1K6-A1</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>-1K6</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1K6-A2</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1K7-A1</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>-1K7</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Сброс</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1K7-A2</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>1K8-A1</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>-1K8</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nДатчик метки\nот автомата Bosch1</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1K8-A2</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>1K9-A1</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>-1K1</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Факт печати</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>1K9-A2</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>1K10-A1</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>-1K2</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Интерлок</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>1K10-A2</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1K11-11</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>-1K11</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nСигнал останова\nавтомат Bosch1</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>+24V</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>1K11-14</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>1K12-11</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>-1K12</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nWatchDog\nавтомата Bosch1</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>1K12-14</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>1K13-11</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>-1K13</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1K13-14</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>1K14-11</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>-1K14</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>1K14-14</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1K15-11</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>-1K15</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>1K15-14</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>+ZM</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>W1CPW2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FLEXICORE 130H нг(A)-HF 10G0,75</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-CC_CPW</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2K5-A1</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>-2K5</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nСигнал готовности\nавтомата Bosch2</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>0V</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2K5-A2</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2K6-A1</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>-2K6</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2K6-A2</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2K7-A1</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>-2K7</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>=24V</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Сброс</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2K7-A2</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2K8-A1</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>-2K8</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nДатчик метки\nот автомата Bosch2</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2K8-A2</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2K9-A1</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>-2K1</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Факт печати</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2K9-A2</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2K10-A1</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>катушка</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>-2K2</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>=24В,\nТТР</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Интерлок</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2K10-A2</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2K11-11</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>-2K11</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nСигнал останова\nавтомат Bosch2</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>+24V</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2K11-14</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2K12-11</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>-2K12</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Шкаф CPW\nWatchDog\nавтомата Bosch2</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2K12-14</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2K13-11</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>-2K13</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2K13-14</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2K14-11</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>-2K14</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2K14-14</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2K15-11</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>контакт</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>-2K15</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3XT1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2K15-14</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3236,7 +9365,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6927d804b312035e06b59c795d67885a</t>
+          <t>20767cc852c43ad9b7fb9f8b3e253ca6</t>
         </is>
       </c>
     </row>
@@ -3259,7 +9388,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>e8c79e456e4d12a298f91f17f6b50bc5</t>
+          <t>f0c06dacb76aef5f863294287cc663e7</t>
         </is>
       </c>
     </row>
@@ -3275,8 +9404,16 @@
           <t>2196_SS1.pdf</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fields:0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>24fb284686d94da7165cec6d9482353c</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3290,8 +9427,16 @@
           <t>2196_SS1.pdf</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>fields:1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21d45b7e257e73a3192fa7cb5c62dd9a</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3305,8 +9450,16 @@
           <t>2196_SS1.pdf</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>fields:2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16be4170bbedd91efb1811481134f6de</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3320,15 +9473,23 @@
           <t>2196_SS1.pdf</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fields:3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>f579052cb4a0f5487d0d9e5e71bdf1cf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10823,7 +16984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10837,6 +16998,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10893,6 +17055,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Выходы NPN</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Раскладка</t>
         </is>
       </c>
     </row>
@@ -10928,6 +17095,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>A1=260.8; A2=325.9; A3=388.3; A4=447.9; A5=660.5; A6=728.5; A7=796.6; A8=864.6; A9=1040.4</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10981,6 +17153,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>B1=192.8; B2=294.9; B3=396.9; B4=498.9; B5=601; B6=703; B7=805.1; B8=907.2; B9=975.2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11030,6 +17207,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11075,6 +17253,7 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11120,6 +17299,7 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11165,6 +17345,7 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/example_2196_SS1.xlsx
+++ b/examples/example_2196_SS1.xlsx
@@ -19,8 +19,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сеть" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабели сети" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Коробки" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Колонна" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9217,6 +9218,431 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Реле</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Марка провода</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Цвет провода</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Провод от реле</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Через контакт</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Выводы контакта</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>колонна</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Сигнальная колонна</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-HL1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>питание</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1QFU5-1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-1K1:13+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>сегмент</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>лампа</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-K1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>HL1-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>сегмент</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>YL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>лампа</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-K2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HL1-2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>сегмент</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>лампа</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-K3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HL1-3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>K3-14 / WH / 0,5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-KBF1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11/14/12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>/2.6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>сегмент</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>зуммер</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-K4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HL1-4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>K4-14 / WH / 0,5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-KBF1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21/24/22</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>/2.6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>общий</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>XM1-M3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DK BU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-XM1:M3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9365,7 +9791,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20767cc852c43ad9b7fb9f8b3e253ca6</t>
+          <t>08b61cc82de5e7cc64c385599632ec05</t>
         </is>
       </c>
     </row>
@@ -9383,12 +9809,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>plc:CPU.DO</t>
+          <t>plc:CPU.DO, column</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>f0c06dacb76aef5f863294287cc663e7</t>
+          <t>d8bcfc52ccdad5e2e884dd1fa6422d58</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17097,7 +17523,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>A1=260.8; A2=325.9; A3=388.3; A4=447.9; A5=660.5; A6=728.5; A7=796.6; A8=864.6; A9=1040.4</t>
+          <t>x0=198.4; x1=1097; top=609.6; h=147.4; desc=61.8; mark=28.4; tip=503.8; com_y=553.1; com_dx=22.5; A1=260.8; A2=325.9; A3=388.3; A4=447.9; A5=660.5; A6=728.5; A7=796.6; A8=864.6; A9=1040.4</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17581,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>B1=192.8; B2=294.9; B3=396.9; B4=498.9; B5=601; B6=703; B7=805.1; B8=907.2; B9=975.2</t>
+          <t>x0=133.2; x1=1003.5; top=73.8; h=119.1; desc=52.1; mark=42.5; pin=21.9; coil=68; bus=110.5; ret=147.4; mir=7.2; ret_tip=45.4; B1=192.8; B2=294.9; B3=396.9; B4=498.9; B5=601; B6=703; B7=805.1; B8=907.2; B9=975.2</t>
         </is>
       </c>
     </row>
